--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -1,50 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,85 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -216,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -284,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -419,109 +351,581 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D37"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Household ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Representative Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Points</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Hardship Adjustment</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Household ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Representative Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Points</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Hardship Adjustment</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HH-000</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>[SAMPLE PARENT]</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
+      <c r="A2" t="str">
+        <v>HH-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MATEO ASUMEN BOBILES</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Standard</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HH-001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>MATEO ASUMEN BOBILES</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
+      <c r="A3" t="str">
+        <v>HH-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>JUNRISH EBUENGA CAONES</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Solo Parent</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HH-002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>JUNRISH EBUENGA CAONES</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Solo Parent</t>
-        </is>
+      <c r="A4" t="str">
+        <v>HH-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>RICHLYN LANDICHO CAPULO</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>HH-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>FRANCIS ALLESANDRO CASPE CUSTODIO</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HH-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>REYNIEL ALLEN ROBLES ESCUETA</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <v>OFW</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HH-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>JOHN CARLO BARRUGA LAZANAS</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HH-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PHILIP ANDREW CABALLERO LOGRONIO</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HH-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>CANDICE BARLOLAY MOSQUERA</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Solo Parent</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HH-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>RHEAN MARK MAGANA PACHECO</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HH-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AKEESHA LIANNE ALCAZAR ROSALES</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HH-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>JOSHUA DAVID RELLATORRES ROSAS</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HH-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>VINCE ARON SANGALANG SUGUITAN</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HH-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>TRICIA YHANIE ABITO BIEN</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HH-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>KRIZZEL CADE AUSTRIA DERLA</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Solo Parent</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HH-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>HERSHEY MHAORI HERNANDEZ</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HH-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>RHAYNE LUMAG MARTINEZ</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HH-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>KEISHA BRICE PANOPIO MELEGRITO</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HH-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>KYLE BRENAN SAGADRACA MENDOZA</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HH-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>NICOLE ANNE UROT SABAL</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="str">
+        <v>OFW</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HH-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>AIKEE MIKAELA MIRANDUQUE SANTOS</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HH-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>QUIM DRIZEL QUIMIO TOLENTINO</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HH-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>XYRA HYACINTH RODRIGUEZ CLEOPAS</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HH-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SAMANTHA RAGODON ECRAELA</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HH-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>FAITH EUNICE FAMILIAR FLORES</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HH-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ERIC JOSH SANTIAGO GARCIA</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Solo Parent</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HH-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>ANGELU T. NUMERON</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HH-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>NASH IVAN RAFALLO PANTOJA</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HH-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>ALLYN BAUTISTA RONDINA</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HH-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>HANNA KIMBERLIE VALERA FERNANDEZ</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HH-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>ANYA NATALIE HERNANDEZ DETRUZ</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HH-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>RHAINE JANNELLE SUA NACIONALES</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HH-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ANDREA NICOLE PAR MERCADO</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HH-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>GRACE ANUYO UMALI</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HH-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>EUSSEY AOE SAN JUAN DEINLA</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HH-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ARVEL NICOLE TERCERO UMALI</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Solo Parent</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HH-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>FRANCHESCA LUBANG SISCON</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Standard</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
+  </ignoredErrors>
 </worksheet>
 </file>